--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,9 +439,26 @@
         <v>Submitted At</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>6d12568c-e6b2-4190-8a80-58ef5b3604ac</v>
+      </c>
+      <c r="B2" t="str">
+        <v>LMIS</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Logistics Management Information System</v>
+      </c>
+      <c r="D2" t="str">
+        <v>pending</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-10-15T06:11:13.949Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -411,9 +411,20 @@
         <v>Meaning</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>LMIS</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Logistics Management Information System</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -450,7 +461,7 @@
         <v>Logistics Management Information System</v>
       </c>
       <c r="D2" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="E2" t="str">
         <v>2026-10-15T06:11:13.949Z</v>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -467,9 +467,26 @@
         <v>2026-10-15T06:11:13.949Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>642e382a-4d22-4321-b9f7-2a02bb8b785c</v>
+      </c>
+      <c r="B3" t="str">
+        <v>HMIS</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Health Management Information System</v>
+      </c>
+      <c r="D3" t="str">
+        <v>pending</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-10-16T09:18:24.759Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,9 +422,20 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>HMIS</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Health Management Information System</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -478,7 +489,7 @@
         <v>Health Management Information System</v>
       </c>
       <c r="D3" t="str">
-        <v>pending</v>
+        <v>approved</v>
       </c>
       <c r="E3" t="str">
         <v>2026-10-16T09:18:24.759Z</v>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -430,7 +430,7 @@
         <v>Health Management Information System</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>a structured digital or routine information framework that collects, stores, analyzes, and evaluates health-related data from medical facilities to administrative, regional, and national levels</v>
       </c>
     </row>
   </sheetData>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -419,7 +419,7 @@
         <v>Logistics Management Information System</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>A logistics management information system (LMIS) is a system of records and reports – whether paper-based or electronic – used to aggregate, analyze, validate and display data from all levels of the supply chain system that can be used to make logistics decisions and manage the supply chain.</v>
       </c>
     </row>
     <row r="3">

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,20 @@
         <v>a structured digital or routine information framework that collects, stores, analyzes, and evaluates health-related data from medical facilities to administrative, regional, and national levels</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CHP</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Community Health Promoter</v>
+      </c>
+      <c r="C4" t="str">
+        <v>A Community Health Promoter (CHP) acts as the critical last-mile distributor in the public health supply chain, delivering essential medical commodities directly to households in underserved areas. In East Africa, logisticians and health managers rely on the consumption data and stock reports generated by CHPs to forecast demand for items like malaria rapid diagnostic tests, family planning products, and basic medicines. By effectively managing these village-level micro-inventories, CHPs ensure continuous product availability and prevent stockouts where traditional health facilities are inaccessible</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,9 +444,20 @@
         <v>A Community Health Promoter (CHP) acts as the critical last-mile distributor in the public health supply chain, delivering essential medical commodities directly to households in underserved areas. In East Africa, logisticians and health managers rely on the consumption data and stock reports generated by CHPs to forecast demand for items like malaria rapid diagnostic tests, family planning products, and basic medicines. By effectively managing these village-level micro-inventories, CHPs ensure continuous product availability and prevent stockouts where traditional health facilities are inaccessible</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CHW</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Community Health Workers</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Community Health Workers (CHWs) serve as the essential link between formal health facilities and community-level product distribution, often acting as the final dispensing point for basic medicines and health commodities. Governments and development partners depend on the localized consumption data reported by CHWs to calculate accurate resupply quantities and prevent stockouts of critical items like antimalarials and nutritional supplements. By decentralizing this last mile of the supply chain, CHWs ensure life-saving products reliably reach remote or marginalized populations across East Africa.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -455,9 +455,20 @@
         <v>Community Health Workers (CHWs) serve as the essential link between formal health facilities and community-level product distribution, often acting as the final dispensing point for basic medicines and health commodities. Governments and development partners depend on the localized consumption data reported by CHWs to calculate accurate resupply quantities and prevent stockouts of critical items like antimalarials and nutritional supplements. By decentralizing this last mile of the supply chain, CHWs ensure life-saving products reliably reach remote or marginalized populations across East Africa.</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Lead Time</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Lead Time (LT) is the total duration between placing an order for medical commodities and their arrival ready for dispensing at a health facility or central warehouse. In East African public health systems, logisticians and supply chain managers use accurate LT calculations to determine precise reorder points, factoring in variables like international shipping, customs clearance, and last-mile transport delays. Mastering this metric is critical to preventing life-threatening stockouts of essential medicines while avoiding the costly expiration of overstocked inventory.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,9 +466,20 @@
         <v>Lead Time (LT) is the total duration between placing an order for medical commodities and their arrival ready for dispensing at a health facility or central warehouse. In East African public health systems, logisticians and supply chain managers use accurate LT calculations to determine precise reorder points, factoring in variables like international shipping, customs clearance, and last-mile transport delays. Mastering this metric is critical to preventing life-threatening stockouts of essential medicines while avoiding the costly expiration of overstocked inventory.</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>OOS</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Out Of Stock/Stockouts.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>An Out of Stock (OOS) event occurs when a health facility or warehouse completely depletes its inventory of a specific medical commodity, directly preventing patients from receiving necessary care. Supply chain managers and governments track OOS rates as a critical key performance indicator to identify systemic bottlenecks in forecasting, procurement, or last-mile distribution across East African health systems. Minimizing these stockouts is the ultimate objective of health logistics, as the continuous availability of essential medicines like antimalarials and vaccines is vital for saving lives and sustaining positive public health outcomes.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -471,7 +471,7 @@
         <v>OOS</v>
       </c>
       <c r="B7" t="str">
-        <v>Out Of Stock/Stockouts.</v>
+        <v>Out Of Stock / Stockout.</v>
       </c>
       <c r="C7" t="str">
         <v>An Out of Stock (OOS) event occurs when a health facility or warehouse completely depletes its inventory of a specific medical commodity, directly preventing patients from receiving necessary care. Supply chain managers and governments track OOS rates as a critical key performance indicator to identify systemic bottlenecks in forecasting, procurement, or last-mile distribution across East African health systems. Minimizing these stockouts is the ultimate objective of health logistics, as the continuous availability of essential medicines like antimalarials and vaccines is vital for saving lives and sustaining positive public health outcomes.</v>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,9 +477,20 @@
         <v>An Out of Stock (OOS) event occurs when a health facility or warehouse completely depletes its inventory of a specific medical commodity, directly preventing patients from receiving necessary care. Supply chain managers and governments track OOS rates as a critical key performance indicator to identify systemic bottlenecks in forecasting, procurement, or last-mile distribution across East African health systems. Minimizing these stockouts is the ultimate objective of health logistics, as the continuous availability of essential medicines like antimalarials and vaccines is vital for saving lives and sustaining positive public health outcomes.</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NLMIS</v>
+      </c>
+      <c r="B8" t="str">
+        <v>National Logistics Management Information System</v>
+      </c>
+      <c r="C8" t="str">
+        <v>The National Logistics Management Information System (NLMIS) is a centralized digital platform used by Ministries of Health and logisticians to track the flow of medical commodities from central medical stores down to local health facilities. In East Africa, this system provides critical end-to-end visibility into stock levels, consumption rates, and order fulfillment across the entire public health network. By leveraging NLMIS data, governments and development partners can make evidence-based forecasting and procurement decisions, ensuring equitable distribution of essential medicines and rapidly responding to impending stockouts before they impact patient care.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/abbreviations.xlsx
+++ b/data/abbreviations.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -488,9 +488,20 @@
         <v>The National Logistics Management Information System (NLMIS) is a centralized digital platform used by Ministries of Health and logisticians to track the flow of medical commodities from central medical stores down to local health facilities. In East Africa, this system provides critical end-to-end visibility into stock levels, consumption rates, and order fulfillment across the entire public health network. By leveraging NLMIS data, governments and development partners can make evidence-based forecasting and procurement decisions, ensuring equitable distribution of essential medicines and rapidly responding to impending stockouts before they impact patient care.</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DHIS2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>District Health Information Software</v>
+      </c>
+      <c r="C9" t="str">
+        <v>District Health Information Software 2 (DHIS2) is the primary health management information system used by East African Ministries of Health to collect, analyze, and visualize routine clinical and public health data. Supply chain managers and logisticians increasingly integrate DHIS2 service data with logistics platforms to triangulate disease burden against commodity consumption, ensuring that the volume of distributed medicines aligns with actual patient needs. By linking clinical diagnoses to inventory usage, governments and development partners can optimize national forecasting, validate consumption reports, and better allocate resources during localized disease outbreaks.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
